--- a/数据表/Datas/ResourcePointConfig_物资点配置.xlsx
+++ b/数据表/Datas/ResourcePointConfig_物资点配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -38,7 +38,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>lootConfigs</t>
+    <t>*lootConfigs</t>
   </si>
   <si>
     <t>##type</t>
@@ -50,7 +50,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>(list#sep=|),LootGenerationConfig#sep=,</t>
+    <t>list,LootGenerationConfig</t>
   </si>
   <si>
     <t>##group</t>
@@ -59,10 +59,40 @@
     <t>c</t>
   </si>
   <si>
+    <t>difficulty</t>
+  </si>
+  <si>
+    <t>minCount</t>
+  </si>
+  <si>
+    <t>maxCount</t>
+  </si>
+  <si>
+    <t>whiteWeight</t>
+  </si>
+  <si>
+    <t>greenWeight</t>
+  </si>
+  <si>
+    <t>blueWeight</t>
+  </si>
+  <si>
+    <t>goldWeight</t>
+  </si>
+  <si>
+    <t>redWeight</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>物资点类型</t>
     </r>
     <r>
@@ -79,10 +109,37 @@
     <t>显示名</t>
   </si>
   <si>
-    <t>每个难度的数量与五档稀有度权重</t>
+    <t>难度档位</t>
+  </si>
+  <si>
+    <t>最少生成数量</t>
+  </si>
+  <si>
+    <t>最多生成数量</t>
+  </si>
+  <si>
+    <t>白色权重</t>
+  </si>
+  <si>
+    <t>绿色权重</t>
+  </si>
+  <si>
+    <t>蓝色权重</t>
+  </si>
+  <si>
+    <t>金色权重</t>
+  </si>
+  <si>
+    <t>红色权重</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>物资点</t>
     </r>
     <r>
@@ -96,10 +153,22 @@
     </r>
   </si>
   <si>
-    <t>Tier1,1,2,70,25,5,0,0|Tier2,1,3,45,35,15,5,0|Tier3,2,4,20,30,25,15,10</t>
+    <t>Tier1</t>
+  </si>
+  <si>
+    <t>Tier2</t>
+  </si>
+  <si>
+    <t>Tier3</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>物资点</t>
     </r>
     <r>
@@ -113,10 +182,13 @@
     </r>
   </si>
   <si>
-    <t>Tier1,1,2,80,18,2,0,0|Tier2,1,3,55,30,12,3,0|Tier3,2,4,30,30,22,13,5</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>物资点</t>
     </r>
     <r>
@@ -130,10 +202,13 @@
     </r>
   </si>
   <si>
-    <t>Tier1,1,2,50,35,12,3,0|Tier2,2,3,30,35,22,10,3|Tier3,2,4,15,25,30,20,10</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>物资点</t>
     </r>
     <r>
@@ -147,10 +222,13 @@
     </r>
   </si>
   <si>
-    <t>Tier1,1,3,65,25,8,2,0|Tier2,2,4,40,30,20,8,2|Tier3,3,5,20,25,25,20,10</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>物资点</t>
     </r>
     <r>
@@ -163,9 +241,6 @@
       <t>5</t>
     </r>
   </si>
-  <si>
-    <t>Tier1,1,2,30,35,25,8,2|Tier2,2,3,20,30,25,15,10|Tier3,3,5,10,20,25,25,20</t>
-  </si>
 </sst>
 </file>
 
@@ -177,7 +252,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -216,6 +291,12 @@
       <sz val="12"/>
       <color rgb="FF9C0006"/>
       <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Carlito"/>
       <charset val="134"/>
     </font>
     <font>
@@ -382,7 +463,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,18 +520,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -600,7 +669,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -612,6 +681,43 @@
       <left style="thin">
         <color rgb="FF9BBB9B"/>
       </left>
+      <right style="thin">
+        <color rgb="FF9BBB9B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9BBB9B"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BBB9B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BBB9B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF9BBB9B"/>
       </right>
@@ -640,6 +746,43 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF9EBDD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9EBDD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9EBDD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9EBDD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
@@ -648,6 +791,19 @@
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
@@ -783,82 +939,88 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -867,10 +1029,10 @@
     <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -879,10 +1041,10 @@
     <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -891,10 +1053,10 @@
     <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -903,10 +1065,10 @@
     <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -915,63 +1077,81 @@
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1445,133 +1625,644 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.6838235294118" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.6029411764706" style="2" customWidth="1"/>
-    <col min="4" max="4" width="89.5808823529412" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="20.2132352941176" style="3" customWidth="1"/>
+    <col min="5" max="5" width="16.4191176470588" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.9705882352941" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.3161764705882" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.0147058823529" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.1691176470588" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.9705882352941" style="3" customWidth="1"/>
+    <col min="11" max="11" width="15.1985294117647" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+    <row r="1" customHeight="1" spans="1:11">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:11">
+      <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:4">
-      <c r="A3" s="7" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:11">
+      <c r="A3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:4">
-      <c r="A4" s="9" t="s">
+      <c r="E3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:11">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="G4" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:4">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13">
+      <c r="H4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:11">
+      <c r="A5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:11">
+      <c r="A6" s="20"/>
+      <c r="B6" s="21">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="C6" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>70</v>
+      </c>
+      <c r="H6" s="3">
+        <v>25</v>
+      </c>
+      <c r="I6" s="3">
+        <v>5</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:11">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>45</v>
+      </c>
+      <c r="H7" s="3">
+        <v>35</v>
+      </c>
+      <c r="I7" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:4">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13">
+      <c r="J7" s="3">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:11">
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:4">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13">
+      <c r="F8" s="3">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>20</v>
+      </c>
+      <c r="H8" s="3">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3">
+        <v>25</v>
+      </c>
+      <c r="J8" s="3">
+        <v>15</v>
+      </c>
+      <c r="K8" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:11">
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:11">
+      <c r="A10" s="20"/>
+      <c r="B10" s="21">
+        <v>2</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>80</v>
+      </c>
+      <c r="H10" s="3">
+        <v>18</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:11">
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
         <v>3</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:4">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13">
+      <c r="G11" s="3">
+        <v>55</v>
+      </c>
+      <c r="H11" s="3">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3">
+        <v>12</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:11">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
         <v>4</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="G12" s="3">
+        <v>30</v>
+      </c>
+      <c r="H12" s="3">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3">
+        <v>22</v>
+      </c>
+      <c r="J12" s="3">
+        <v>13</v>
+      </c>
+      <c r="K12" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:11">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="21"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:11">
+      <c r="A14" s="20"/>
+      <c r="B14" s="21">
+        <v>3</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2</v>
+      </c>
+      <c r="G14" s="3">
+        <v>50</v>
+      </c>
+      <c r="H14" s="3">
+        <v>35</v>
+      </c>
+      <c r="I14" s="3">
+        <v>12</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:11">
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3">
+        <v>30</v>
+      </c>
+      <c r="H15" s="3">
+        <v>35</v>
+      </c>
+      <c r="I15" s="3">
+        <v>22</v>
+      </c>
+      <c r="J15" s="3">
+        <v>10</v>
+      </c>
+      <c r="K15" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:11">
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4</v>
+      </c>
+      <c r="G16" s="3">
+        <v>15</v>
+      </c>
+      <c r="H16" s="3">
+        <v>25</v>
+      </c>
+      <c r="I16" s="3">
+        <v>30</v>
+      </c>
+      <c r="J16" s="3">
         <v>20</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:4">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13">
+      <c r="K16" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:11">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="21"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
+      <c r="A18" s="20"/>
+      <c r="B18" s="21">
+        <v>4</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3">
+        <v>65</v>
+      </c>
+      <c r="H18" s="3">
+        <v>25</v>
+      </c>
+      <c r="I18" s="3">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:11">
+      <c r="A19" s="20"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>4</v>
+      </c>
+      <c r="H19" s="3">
+        <v>40</v>
+      </c>
+      <c r="I19" s="3">
+        <v>30</v>
+      </c>
+      <c r="J19" s="3">
+        <v>8</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:11">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>5</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>23</v>
+      <c r="H20" s="3">
+        <v>20</v>
+      </c>
+      <c r="I20" s="3">
+        <v>25</v>
+      </c>
+      <c r="J20" s="3">
+        <v>20</v>
+      </c>
+      <c r="K20" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:11">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="21"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21">
+        <v>5</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2</v>
+      </c>
+      <c r="G22" s="3">
+        <v>30</v>
+      </c>
+      <c r="H22" s="3">
+        <v>35</v>
+      </c>
+      <c r="I22" s="3">
+        <v>25</v>
+      </c>
+      <c r="J22" s="3">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:11">
+      <c r="D23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3">
+        <v>20</v>
+      </c>
+      <c r="H23" s="3">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3">
+        <v>25</v>
+      </c>
+      <c r="J23" s="3">
+        <v>15</v>
+      </c>
+      <c r="K23" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:11">
+      <c r="D24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3">
+        <v>25</v>
+      </c>
+      <c r="J24" s="3">
+        <v>25</v>
+      </c>
+      <c r="K24" s="3">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D1:K1"/>
+    <mergeCell ref="D2:K2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/数据表/Datas/ResourcePointConfig_物资点配置.xlsx
+++ b/数据表/Datas/ResourcePointConfig_物资点配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -41,6 +41,9 @@
     <t>*lootConfigs</t>
   </si>
   <si>
+    <t>prefab</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -51,6 +54,9 @@
   </si>
   <si>
     <t>list,LootGenerationConfig</t>
+  </si>
+  <si>
+    <t>string#ref=TbEntityConfig</t>
   </si>
   <si>
     <t>##group</t>
@@ -133,6 +139,9 @@
     <t>红色权重</t>
   </si>
   <si>
+    <t>实体</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -156,6 +165,9 @@
     <t>Tier1</t>
   </si>
   <si>
+    <t>ResourcePoint1</t>
+  </si>
+  <si>
     <t>Tier2</t>
   </si>
   <si>
@@ -182,6 +194,9 @@
     </r>
   </si>
   <si>
+    <t>ResourcePoint2</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -202,6 +217,9 @@
     </r>
   </si>
   <si>
+    <t>ResourcePoint3</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -222,6 +240,9 @@
     </r>
   </si>
   <si>
+    <t>ResourcePoint4</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -240,6 +261,9 @@
       </rPr>
       <t>5</t>
     </r>
+  </si>
+  <si>
+    <t>ResourcePoint5</t>
   </si>
 </sst>
 </file>
@@ -1094,9 +1118,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1153,6 +1174,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1625,636 +1649,663 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.6838235294118" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.6029411764706" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.2132352941176" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.4191176470588" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.9705882352941" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.3161764705882" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18.0147058823529" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16.1691176470588" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.9705882352941" style="3" customWidth="1"/>
-    <col min="11" max="11" width="15.1985294117647" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="20.2132352941176" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.4191176470588" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.9705882352941" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.3161764705882" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.0147058823529" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.1691176470588" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.9705882352941" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.1985294117647" style="2" customWidth="1"/>
+    <col min="12" max="12" width="28.4264705882353" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
-      <c r="A1" s="4" t="s">
+    <row r="1" customHeight="1" spans="1:12">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="8"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="9" t="s">
+    <row r="2" customHeight="1" spans="1:12">
+      <c r="A2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:12">
+      <c r="A3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="14"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:12">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:12">
+      <c r="A5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:12">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20">
+        <v>1</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>70</v>
+      </c>
+      <c r="H6" s="2">
+        <v>25</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:12">
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45</v>
+      </c>
+      <c r="H7" s="2">
+        <v>35</v>
+      </c>
+      <c r="I7" s="2">
+        <v>15</v>
+      </c>
+      <c r="J7" s="2">
+        <v>5</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:12">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2">
         <v>4</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="G8" s="2">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2">
+        <v>25</v>
+      </c>
+      <c r="J8" s="2">
+        <v>15</v>
+      </c>
+      <c r="K8" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:12">
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="20"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:12">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20">
+        <v>2</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2">
+        <v>80</v>
+      </c>
+      <c r="H10" s="2">
+        <v>18</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:12">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2">
+        <v>55</v>
+      </c>
+      <c r="H11" s="2">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2">
+        <v>12</v>
+      </c>
+      <c r="J11" s="2">
+        <v>3</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:12">
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>4</v>
+      </c>
+      <c r="G12" s="2">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2">
+        <v>22</v>
+      </c>
+      <c r="J12" s="2">
+        <v>13</v>
+      </c>
+      <c r="K12" s="2">
         <v>5</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="13"/>
     </row>
-    <row r="3" customHeight="1" spans="1:11">
-      <c r="A3" s="14" t="s">
+    <row r="13" customHeight="1" spans="1:12">
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="20"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:12">
+      <c r="A14" s="19"/>
+      <c r="B14" s="20">
+        <v>3</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2">
+        <v>50</v>
+      </c>
+      <c r="H14" s="2">
+        <v>35</v>
+      </c>
+      <c r="I14" s="2">
+        <v>12</v>
+      </c>
+      <c r="J14" s="2">
+        <v>3</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:12">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2">
+        <v>35</v>
+      </c>
+      <c r="I15" s="2">
+        <v>22</v>
+      </c>
+      <c r="J15" s="2">
+        <v>10</v>
+      </c>
+      <c r="K15" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>4</v>
+      </c>
+      <c r="G16" s="2">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2">
+        <v>25</v>
+      </c>
+      <c r="I16" s="2">
+        <v>30</v>
+      </c>
+      <c r="J16" s="2">
+        <v>20</v>
+      </c>
+      <c r="K16" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:12">
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="20"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:12">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20">
+        <v>4</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3</v>
+      </c>
+      <c r="G18" s="2">
+        <v>65</v>
+      </c>
+      <c r="H18" s="2">
+        <v>25</v>
+      </c>
+      <c r="I18" s="2">
         <v>8</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>9</v>
+      <c r="J18" s="2">
+        <v>2</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
+    <row r="19" customHeight="1" spans="1:12">
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2">
+        <v>4</v>
+      </c>
+      <c r="H19" s="2">
+        <v>40</v>
+      </c>
+      <c r="I19" s="2">
+        <v>30</v>
+      </c>
+      <c r="J19" s="2">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:12">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2">
+        <v>5</v>
+      </c>
+      <c r="H20" s="2">
+        <v>20</v>
+      </c>
+      <c r="I20" s="2">
+        <v>25</v>
+      </c>
+      <c r="J20" s="2">
+        <v>20</v>
+      </c>
+      <c r="K20" s="2">
         <v>10</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="5" t="s">
+    </row>
+    <row r="21" customHeight="1" spans="1:12">
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="20"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:12">
+      <c r="A22" s="19"/>
+      <c r="B22" s="20">
+        <v>5</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2">
+        <v>35</v>
+      </c>
+      <c r="I22" s="2">
+        <v>25</v>
+      </c>
+      <c r="J22" s="2">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2">
+        <v>2</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:12">
+      <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2">
+        <v>25</v>
+      </c>
+      <c r="J23" s="2">
         <v>15</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>17</v>
+      <c r="K23" s="2">
+        <v>10</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="19" t="s">
+    <row r="24" customHeight="1" spans="1:12">
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2">
+        <v>3</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3</v>
+      </c>
+      <c r="G24" s="2">
+        <v>5</v>
+      </c>
+      <c r="H24" s="2">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2">
         <v>25</v>
       </c>
-      <c r="I5" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:11">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21">
-        <v>1</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3">
-        <v>70</v>
-      </c>
-      <c r="H6" s="3">
+      <c r="J24" s="2">
         <v>25</v>
       </c>
-      <c r="I6" s="3">
-        <v>5</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3</v>
-      </c>
-      <c r="G7" s="3">
-        <v>45</v>
-      </c>
-      <c r="H7" s="3">
-        <v>35</v>
-      </c>
-      <c r="I7" s="3">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3">
-        <v>5</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="20"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3">
-        <v>20</v>
-      </c>
-      <c r="H8" s="3">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3">
-        <v>25</v>
-      </c>
-      <c r="J8" s="3">
-        <v>15</v>
-      </c>
-      <c r="K8" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="21"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21">
-        <v>2</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2</v>
-      </c>
-      <c r="G10" s="3">
-        <v>80</v>
-      </c>
-      <c r="H10" s="3">
-        <v>18</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:11">
-      <c r="A11" s="20"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3">
-        <v>3</v>
-      </c>
-      <c r="G11" s="3">
-        <v>55</v>
-      </c>
-      <c r="H11" s="3">
-        <v>30</v>
-      </c>
-      <c r="I11" s="3">
-        <v>12</v>
-      </c>
-      <c r="J11" s="3">
-        <v>3</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:11">
-      <c r="A12" s="20"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3">
-        <v>30</v>
-      </c>
-      <c r="H12" s="3">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3">
-        <v>22</v>
-      </c>
-      <c r="J12" s="3">
-        <v>13</v>
-      </c>
-      <c r="K12" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:11">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="21"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:11">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21">
-        <v>3</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2</v>
-      </c>
-      <c r="G14" s="3">
-        <v>50</v>
-      </c>
-      <c r="H14" s="3">
-        <v>35</v>
-      </c>
-      <c r="I14" s="3">
-        <v>12</v>
-      </c>
-      <c r="J14" s="3">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:11">
-      <c r="A15" s="20"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3">
-        <v>30</v>
-      </c>
-      <c r="H15" s="3">
-        <v>35</v>
-      </c>
-      <c r="I15" s="3">
-        <v>22</v>
-      </c>
-      <c r="J15" s="3">
-        <v>10</v>
-      </c>
-      <c r="K15" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:11">
-      <c r="A16" s="20"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="3">
-        <v>2</v>
-      </c>
-      <c r="F16" s="3">
-        <v>4</v>
-      </c>
-      <c r="G16" s="3">
-        <v>15</v>
-      </c>
-      <c r="H16" s="3">
-        <v>25</v>
-      </c>
-      <c r="I16" s="3">
-        <v>30</v>
-      </c>
-      <c r="J16" s="3">
-        <v>20</v>
-      </c>
-      <c r="K16" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="20"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="21"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="20"/>
-      <c r="B18" s="21">
-        <v>4</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3">
-        <v>65</v>
-      </c>
-      <c r="H18" s="3">
-        <v>25</v>
-      </c>
-      <c r="I18" s="3">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
-        <v>2</v>
-      </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:11">
-      <c r="A19" s="20"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="3">
-        <v>2</v>
-      </c>
-      <c r="F19" s="3">
-        <v>2</v>
-      </c>
-      <c r="G19" s="3">
-        <v>4</v>
-      </c>
-      <c r="H19" s="3">
-        <v>40</v>
-      </c>
-      <c r="I19" s="3">
-        <v>30</v>
-      </c>
-      <c r="J19" s="3">
-        <v>8</v>
-      </c>
-      <c r="K19" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:11">
-      <c r="A20" s="20"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="3">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3">
-        <v>20</v>
-      </c>
-      <c r="I20" s="3">
-        <v>25</v>
-      </c>
-      <c r="J20" s="3">
-        <v>20</v>
-      </c>
-      <c r="K20" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:11">
-      <c r="A21" s="20"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="21"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="20"/>
-      <c r="B22" s="21">
-        <v>5</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2</v>
-      </c>
-      <c r="G22" s="3">
-        <v>30</v>
-      </c>
-      <c r="H22" s="3">
-        <v>35</v>
-      </c>
-      <c r="I22" s="3">
-        <v>25</v>
-      </c>
-      <c r="J22" s="3">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:11">
-      <c r="D23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2</v>
-      </c>
-      <c r="F23" s="3">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3">
-        <v>20</v>
-      </c>
-      <c r="H23" s="3">
-        <v>30</v>
-      </c>
-      <c r="I23" s="3">
-        <v>25</v>
-      </c>
-      <c r="J23" s="3">
-        <v>15</v>
-      </c>
-      <c r="K23" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:11">
-      <c r="D24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="3">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
-        <v>5</v>
-      </c>
-      <c r="H24" s="3">
-        <v>10</v>
-      </c>
-      <c r="I24" s="3">
-        <v>25</v>
-      </c>
-      <c r="J24" s="3">
-        <v>25</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="K24" s="2">
         <v>20</v>
       </c>
     </row>
